--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11851,7 +11869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11895,6 +11913,93 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1999_00_0263 'Náchod B' prev→CLUB_S1998_99_0291 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1999_00_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1999_00_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0021</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1999_00_0021 'Baráž o Extraligu' (L15, parent=NODE_S1999_00_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0028</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1999_00_0028 'Baráž o I.ligu' (L25, parent=NODE_S1999_00_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0047</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1999_00_0047 'O postup do I.ligy' (L25, parent=NODE_S1999_00_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -16139,8 +16244,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -16220,7 +16323,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -33770,6 +33872,193 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0263</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0263 'Náchod B' prev→CLUB_S1998_99_0291 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0029</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0030</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0021</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1999_00_0021 'Baráž o Extraligu' (L15, parent=NODE_S1999_00_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0028</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1999_00_0028 'Baráž o I.ligu' (L25, parent=NODE_S1999_00_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0047</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1999_00_0047 'O postup do I.ligy' (L25, parent=NODE_S1999_00_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11869,7 +11869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11919,7 +11919,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1999_00_0263 'Náchod B' prev→CLUB_S1998_99_0291 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -11931,7 +11931,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1999_00_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11943,7 +11943,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1999_00_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11953,14 +11953,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0021</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1999_00_0021 'Baráž o Extraligu' (L15, parent=NODE_S1999_00_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11970,14 +11965,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0028</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1999_00_0028 'Baráž o I.ligu' (L25, parent=NODE_S1999_00_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11987,17 +11977,476 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0047</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1999_00_0047 'O postup do I.ligy' (L25, parent=NODE_S1999_00_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Louny' → 'PSV Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Ústí nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0030</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0031</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0032</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0033</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16244,6 +16693,8 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -16274,6 +16725,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0001</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -16286,6 +16742,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0003</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -16298,6 +16759,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0003</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16310,6 +16776,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0041</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16323,6 +16794,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -19110,12 +19582,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -19194,12 +19666,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -19582,12 +20054,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -19886,12 +20358,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -20096,12 +20568,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -20185,12 +20657,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -20264,12 +20736,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -20333,12 +20805,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný.</t>
+          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný. || TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>HK Lev Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -21074,12 +21546,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -21378,12 +21850,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -21420,12 +21892,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -21504,12 +21976,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -21751,12 +22223,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný.</t>
+          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný. || TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>HK Lev Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -21793,12 +22265,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -22003,12 +22475,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -22680,12 +23152,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -23874,12 +24346,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -23958,12 +24430,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -24210,12 +24682,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -24294,12 +24766,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -24467,12 +24939,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -24514,12 +24986,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -27431,12 +27903,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -28415,12 +28887,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -28583,12 +29055,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: city 'Louny' → 'PSV Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Louny</t>
+          <t>PSV Litoměřice</t>
         </is>
       </c>
     </row>
@@ -28625,12 +29097,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Ústí nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -28667,12 +29139,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -29646,12 +30118,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -31611,12 +32083,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = HC Florida Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. Post-revolucni nazev. city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = HC Florida Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. Post-revolucni nazev. city Velké Meziříčí. || TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Florida Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -33349,12 +33821,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře.</t>
+          <t>Kravaře = HC Buly Centrum Kravaře (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). city Kravaře. || TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Buly Centrum Kravaře</t>
+          <t>Kravaře</t>
         </is>
       </c>
     </row>
@@ -33882,11 +34354,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -33931,21 +34403,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0263</t>
+          <t>CLUB_S1999_00_0004</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0263 'Náchod B' prev→CLUB_S1998_99_0291 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -33953,21 +34423,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0029</t>
+          <t>CLUB_S1999_00_0006</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0029 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -33975,21 +34443,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0030</t>
+          <t>CLUB_S1999_00_0015</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0030 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -33997,21 +34463,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1999_00_0021</t>
+          <t>CLUB_S1999_00_0022</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1999_00_0021 'Baráž o Extraligu' (L15, parent=NODE_S1999_00_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -34019,21 +34483,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NODE_S1999_00_0028</t>
+          <t>CLUB_S1999_00_0027</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1999_00_0028 'Baráž o I.ligu' (L25, parent=NODE_S1999_00_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -34041,24 +34503,762 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NODE_S1999_00_0047</t>
+          <t>CLUB_S1999_00_0029</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1999_00_0047 'O postup do I.ligy' (L25, parent=NODE_S1999_00_0041) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0031</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0034</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0058</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0066</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0067</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0069</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0075</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0076</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0082</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0098</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0127</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0129</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0129</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0135</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0137</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0141</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0142</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0209</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0230</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0232</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0236</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0236</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Louny' → 'PSV Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0237</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Ústí nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0238</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0243</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0249</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0261</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0263</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0270</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0275</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0307</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0309</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1999_00_0348</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0030</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0031</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0032</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0033</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54799,6 +55999,11 @@
           <t>CLUB_S1998_99_0273</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>TR_S1999_00_00178</t>
@@ -54844,6 +56049,11 @@
       <c r="R12" t="inlineStr">
         <is>
           <t>CLUB_S1998_99_0274</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -54934,6 +56144,11 @@
           <t>CLUB_S1998_99_0030</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>TR_S1999_00_00180</t>
@@ -55022,6 +56237,11 @@
           <t>CLUB_S1998_99_0274</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>TR_S1999_00_00181</t>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11869,7 +11869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11931,7 +11931,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -11943,7 +11943,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11955,7 +11955,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11967,7 +11967,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11979,7 +11979,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12003,7 +12003,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12015,7 +12015,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12027,7 +12027,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12039,7 +12039,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12051,7 +12051,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12063,7 +12063,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12075,7 +12075,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12087,7 +12087,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12111,7 +12111,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12123,7 +12123,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -12135,7 +12135,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12147,7 +12147,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12159,7 +12159,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12171,7 +12171,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12183,7 +12183,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12195,7 +12195,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12207,7 +12207,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12219,7 +12219,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -12229,9 +12229,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0030</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -12241,9 +12246,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0031</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Louny' → 'PSV Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12253,9 +12263,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0032</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Ústí nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12265,188 +12280,17 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0033</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0030</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0031</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0032</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0033</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -12463,7 +12307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12522,6 +12366,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12564,6 +12413,11 @@
           <t>14 týmů: základ + QF/SF/finále + baráž. Mistr: HC Sparta Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12611,6 +12465,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12653,6 +12512,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12695,6 +12559,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12737,6 +12606,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12779,6 +12653,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12821,6 +12700,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12863,6 +12747,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12905,6 +12794,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12947,6 +12841,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12989,6 +12888,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13031,6 +12935,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13073,6 +12982,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13115,6 +13029,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13157,6 +13076,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13199,6 +13123,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13241,6 +13170,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13283,6 +13217,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -13325,6 +13264,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -13367,6 +13311,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -13409,6 +13358,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -13451,6 +13405,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -13493,6 +13452,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -13535,6 +13499,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -13577,6 +13546,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -13619,6 +13593,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13661,6 +13640,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13750,6 +13734,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0028</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -13782,6 +13771,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0029</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13814,6 +13808,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0030</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -13920,6 +13919,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0031</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -14088,6 +14092,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0034</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -14172,6 +14181,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0036</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -14214,6 +14228,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14256,6 +14275,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14298,6 +14322,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0039</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14340,6 +14369,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0040</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14382,6 +14416,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0041</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14424,6 +14463,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -14466,6 +14510,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -14508,6 +14557,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0044</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -14550,6 +14604,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0045</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -14592,6 +14651,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0046</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -14634,6 +14698,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0047</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -14676,6 +14745,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0048</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -14718,6 +14792,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0049</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14802,6 +14881,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0051</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -14844,6 +14928,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0052</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -14886,6 +14975,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0053</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -14928,6 +15022,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0054</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15138,6 +15237,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0055</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -15180,6 +15284,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0056</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -15222,6 +15331,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0057</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -15264,6 +15378,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0058</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -15684,6 +15803,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0062</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -15726,6 +15850,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0063</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -15936,6 +16065,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0064</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15978,6 +16112,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0065</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16104,6 +16243,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0067</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16146,6 +16290,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0068</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16188,6 +16337,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0069</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16230,6 +16384,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0070</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -16272,6 +16431,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0074</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -16314,6 +16478,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0075</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -16356,6 +16525,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0077</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -16398,6 +16572,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0078</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -16440,6 +16619,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0079</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -16524,6 +16708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0081</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -16650,6 +16839,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0083</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16690,6 +16884,11 @@
       <c r="K101" t="inlineStr">
         <is>
           <t>Kontejner L50</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1998_99_0084</t>
         </is>
       </c>
     </row>
@@ -16713,6 +16912,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -16730,6 +16934,11 @@
           <t>NODE_S1999_00_0001</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -16747,6 +16956,11 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -16764,6 +16978,11 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -16781,6 +17000,11 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -16791,6 +17015,11 @@
       <c r="B110" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -19666,12 +19895,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -20358,12 +20587,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -20736,12 +20965,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -21892,12 +22121,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -22265,12 +22494,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -23152,12 +23381,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24346,12 +24575,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24430,12 +24659,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -24682,12 +24911,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -24766,12 +24995,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29055,12 +29284,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny. || TBD: city 'Louny' → 'PSV Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Louky" → „Louky (UNL)". TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo. || Oprava clean+city: "Louky" → "Louny" (překlep almanachu, Pavlovo upresneni 04/2026 - district "skupina B" v Ústeckém kraji = okres Louny). prev=CLUB_S1951_52_0427 byl chybný (ukazoval na Karviná) - k overeni Pavlem. || Louny = Slovan Louny (Wiki D42 - registr ustavy 04/2026). Hlavni okresni klub. Genealogie: Cechie Louny (49/50) -&gt; VSJ -&gt; Slovan Louny. city Louny.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>PSV Litoměřice</t>
+          <t>Louny</t>
         </is>
       </c>
     </row>
@@ -29097,12 +29326,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Ústí nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -30118,12 +30347,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Nový Bydžov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -34354,7 +34583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -34428,12 +34657,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0006</t>
+          <t>CLUB_S1999_00_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34448,12 +34677,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0015</t>
+          <t>CLUB_S1999_00_0027</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34468,12 +34697,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0022</t>
+          <t>CLUB_S1999_00_0029</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34488,12 +34717,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0027</t>
+          <t>CLUB_S1999_00_0034</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34508,12 +34737,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0029</t>
+          <t>CLUB_S1999_00_0058</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34528,12 +34757,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0031</t>
+          <t>CLUB_S1999_00_0066</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34548,12 +34777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0034</t>
+          <t>CLUB_S1999_00_0069</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34568,12 +34797,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0058</t>
+          <t>CLUB_S1999_00_0075</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34588,12 +34817,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0066</t>
+          <t>CLUB_S1999_00_0082</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34608,12 +34837,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0067</t>
+          <t>CLUB_S1999_00_0129</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34628,12 +34857,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0069</t>
+          <t>CLUB_S1999_00_0141</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34648,12 +34877,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0075</t>
+          <t>CLUB_S1999_00_0142</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34668,12 +34897,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0076</t>
+          <t>CLUB_S1999_00_0209</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34688,12 +34917,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0082</t>
+          <t>CLUB_S1999_00_0230</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -34708,12 +34937,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0098</t>
+          <t>CLUB_S1999_00_0232</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34728,12 +34957,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0127</t>
+          <t>CLUB_S1999_00_0236</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -34748,12 +34977,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0129</t>
+          <t>CLUB_S1999_00_0238</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34768,12 +34997,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0129</t>
+          <t>CLUB_S1999_00_0243</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -34788,12 +35017,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0135</t>
+          <t>CLUB_S1999_00_0249</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -34808,12 +35037,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0137</t>
+          <t>CLUB_S1999_00_0263</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -34828,12 +35057,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0141</t>
+          <t>CLUB_S1999_00_0270</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -34848,12 +35077,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0142</t>
+          <t>CLUB_S1999_00_0275</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -34868,12 +35097,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0209</t>
+          <t>CLUB_S1999_00_0307</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34888,12 +35117,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0230</t>
+          <t>CLUB_S1999_00_0309</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -34908,12 +35137,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0232</t>
+          <t>CLUB_S1999_00_0348</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -34923,17 +35152,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0236</t>
+          <t>NODE_S1999_00_0030</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
     </row>
@@ -34943,17 +35172,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0236</t>
+          <t>NODE_S1999_00_0031</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Louny' → 'PSV Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
     </row>
@@ -34963,17 +35192,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0237</t>
+          <t>NODE_S1999_00_0032</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Teplice' → 'Ústí nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -34983,282 +35212,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1999_00_0238</t>
+          <t>NODE_S1999_00_0033</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0243</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0249</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0261</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0263</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0270</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0275</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0307</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0309</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1999_00_0348</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0030</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0031</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0032</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0033</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -11869,7 +11869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11917,33 +11917,43 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] HC Berounští Medvědi "B" — odstoupily</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] TJ Tatran Sedlčany — odstoupily</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -11955,7 +11965,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -11967,7 +11977,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -11979,7 +11989,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -11991,7 +12001,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -12003,7 +12013,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -12015,7 +12025,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12027,7 +12037,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12039,7 +12049,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -12051,7 +12061,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -12063,7 +12073,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12075,7 +12085,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -12087,7 +12097,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12099,7 +12109,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12135,7 +12145,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -12147,7 +12157,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12159,7 +12169,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12171,7 +12181,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12183,7 +12193,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12195,7 +12205,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -12207,7 +12217,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12219,41 +12229,31 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0030</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NODE_S1999_00_0031</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12265,12 +12265,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NODE_S1999_00_0032</t>
+          <t>NODE_S1999_00_0030</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12282,15 +12282,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>NODE_S1999_00_0031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>NODE_S1999_00_0033</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -46308,7 +46342,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Regionální soutěž / HC Berounští Medvědi "B" — odstoupily</t>
+          <t>Regionální soutěž</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -46341,7 +46375,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Regionální soutěž / TJ Tatran Sedlčany — odstoupily</t>
+          <t>Regionální soutěž</t>
         </is>
       </c>
       <c r="C34" s="2" t="n"/>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -38135,7 +38135,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" t="n">
         <v>54</v>
@@ -38288,7 +38288,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>15</v>
       </c>
       <c r="J10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M10" t="n">
         <v>41</v>
@@ -38839,7 +38839,7 @@
         <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M14" t="n">
         <v>38</v>
@@ -39068,7 +39068,7 @@
         <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -39076,7 +39076,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M17" t="n">
         <v>34</v>
@@ -39536,7 +39536,7 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M23" t="n">
         <v>22</v>
@@ -40228,7 +40228,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M38" t="n">
         <v>51</v>
@@ -40376,7 +40376,7 @@
         <v>18</v>
       </c>
       <c r="J40" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -12341,7 +12341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12405,6 +12405,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16926,8 +16936,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -17057,7 +17065,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -12593,6 +12593,16 @@
           <t>NODE_S1999_00_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12607,6 +12617,14 @@
         <is>
           <t>NODE_S1998_99_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -12781,6 +12799,16 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12795,6 +12823,14 @@
         <is>
           <t>NODE_S1998_99_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -12875,6 +12911,16 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12889,6 +12935,14 @@
         <is>
           <t>NODE_S1998_99_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -12922,6 +12976,16 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12936,6 +13000,14 @@
         <is>
           <t>NODE_S1998_99_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -12969,6 +13041,8 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12983,6 +13057,14 @@
         <is>
           <t>NODE_S1998_99_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -13016,6 +13098,8 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13030,6 +13114,14 @@
         <is>
           <t>NODE_S1998_99_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -13063,6 +13155,8 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13077,6 +13171,14 @@
         <is>
           <t>NODE_S1998_99_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -13110,6 +13212,8 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13124,6 +13228,14 @@
         <is>
           <t>NODE_S1998_99_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -13157,6 +13269,8 @@
           <t>NODE_S1999_00_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13171,6 +13285,14 @@
         <is>
           <t>NODE_S1998_99_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -13204,6 +13326,8 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13218,6 +13342,14 @@
         <is>
           <t>NODE_S1998_99_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -13251,6 +13383,8 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13265,6 +13399,14 @@
         <is>
           <t>NODE_S1998_99_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -13298,6 +13440,16 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13312,6 +13464,14 @@
         <is>
           <t>NODE_S1998_99_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -13439,6 +13599,16 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13453,6 +13623,14 @@
         <is>
           <t>NODE_S1998_99_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -13486,6 +13664,16 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13500,6 +13688,14 @@
         <is>
           <t>NODE_S1998_99_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -13533,6 +13729,12 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13547,6 +13749,14 @@
         <is>
           <t>NODE_S1998_99_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -13580,6 +13790,12 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13594,6 +13810,14 @@
         <is>
           <t>NODE_S1998_99_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -13627,6 +13851,8 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13641,6 +13867,14 @@
         <is>
           <t>NODE_S1998_99_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -13674,6 +13908,8 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13688,6 +13924,14 @@
         <is>
           <t>NODE_S1998_99_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -14126,6 +14370,12 @@
           <t>NODE_S1999_00_0036</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0039</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14140,6 +14390,14 @@
         <is>
           <t>NODE_S1998_99_0034</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -14173,6 +14431,8 @@
           <t>NODE_S1999_00_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14182,6 +14442,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -14215,6 +14483,8 @@
           <t>NODE_S1999_00_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14229,6 +14499,14 @@
         <is>
           <t>NODE_S1998_99_0036</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -14403,6 +14681,12 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0045</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14417,6 +14701,14 @@
         <is>
           <t>NODE_S1998_99_0040</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -14450,6 +14742,12 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0046</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14464,6 +14762,14 @@
         <is>
           <t>NODE_S1998_99_0041</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -14497,6 +14803,8 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14511,6 +14819,14 @@
         <is>
           <t>NODE_S1998_99_0042</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -14638,6 +14954,8 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14652,6 +14970,14 @@
         <is>
           <t>NODE_S1998_99_0045</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -14826,6 +15152,16 @@
           <t>NODE_S1999_00_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0054</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0055</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14840,6 +15176,14 @@
         <is>
           <t>NODE_S1998_99_0049</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -14873,6 +15217,8 @@
           <t>NODE_S1999_00_0051</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14882,6 +15228,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -14915,6 +15269,8 @@
           <t>NODE_S1999_00_0051</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14929,6 +15285,14 @@
         <is>
           <t>NODE_S1998_99_0051</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -15103,6 +15467,12 @@
           <t>NODE_S1999_00_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0060</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15112,6 +15482,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -15145,6 +15523,12 @@
           <t>NODE_S1999_00_0057</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0061</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15154,6 +15538,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -15187,6 +15579,12 @@
           <t>NODE_S1999_00_0057</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0062</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15196,6 +15594,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -15229,6 +15635,8 @@
           <t>NODE_S1999_00_0057</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15238,6 +15646,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -15501,6 +15917,16 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0069</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0070</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15510,6 +15936,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -15543,6 +15977,8 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15552,6 +15988,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -15585,6 +16029,8 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15594,6 +16040,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -15669,6 +16123,16 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0069</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0070</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15678,6 +16142,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -15711,6 +16183,8 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15720,6 +16194,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -15753,6 +16235,8 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15762,6 +16246,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -15931,6 +16423,12 @@
           <t>NODE_S1999_00_0076</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0079</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15940,6 +16438,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -15973,6 +16479,16 @@
           <t>NODE_S1999_00_0076</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0081</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0080</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15982,6 +16498,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -16015,6 +16539,8 @@
           <t>NODE_S1999_00_0076</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16024,6 +16550,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -16057,6 +16591,8 @@
           <t>NODE_S1999_00_0076</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16066,6 +16602,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -16193,6 +16737,12 @@
           <t>NODE_S1999_00_0082</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0087</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16202,6 +16752,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -16235,6 +16793,12 @@
           <t>NODE_S1999_00_0082</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0087</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16244,6 +16808,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -16324,6 +16896,8 @@
           <t>NODE_S1999_00_0082</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16338,6 +16912,14 @@
         <is>
           <t>NODE_S1998_99_0068</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -16559,6 +17141,16 @@
           <t>NODE_S1999_00_0090</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0093</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0094</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16573,6 +17165,14 @@
         <is>
           <t>NODE_S1998_99_0077</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -16606,6 +17206,8 @@
           <t>NODE_S1999_00_0090</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16620,6 +17222,14 @@
         <is>
           <t>NODE_S1998_99_0078</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -16653,6 +17263,8 @@
           <t>NODE_S1999_00_0090</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16667,6 +17279,14 @@
         <is>
           <t>NODE_S1998_99_0079</t>
         </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -16936,6 +17556,8 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -17065,6 +17687,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -753,6 +753,11 @@
           <t>HC Sparta Praha (C)</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -13041,8 +13046,6 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13098,8 +13101,6 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13155,8 +13156,6 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13212,8 +13211,6 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13269,8 +13266,6 @@
           <t>NODE_S1999_00_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13326,8 +13321,6 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13383,8 +13376,6 @@
           <t>NODE_S1999_00_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13734,7 +13725,6 @@
           <t>NODE_S1999_00_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13795,7 +13785,6 @@
           <t>NODE_S1999_00_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13851,8 +13840,6 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13908,8 +13895,6 @@
           <t>NODE_S1999_00_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14375,7 +14360,6 @@
           <t>NODE_S1999_00_0039</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14431,8 +14415,6 @@
           <t>NODE_S1999_00_0036</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14483,8 +14465,6 @@
           <t>NODE_S1999_00_0036</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14686,7 +14666,6 @@
           <t>NODE_S1999_00_0045</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14747,7 +14726,6 @@
           <t>NODE_S1999_00_0046</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14803,8 +14781,6 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14954,8 +14930,6 @@
           <t>NODE_S1999_00_0041</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15217,8 +15191,6 @@
           <t>NODE_S1999_00_0051</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15269,8 +15241,6 @@
           <t>NODE_S1999_00_0051</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15472,7 +15442,6 @@
           <t>NODE_S1999_00_0060</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15528,7 +15497,6 @@
           <t>NODE_S1999_00_0061</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15584,7 +15552,6 @@
           <t>NODE_S1999_00_0062</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15635,8 +15602,6 @@
           <t>NODE_S1999_00_0057</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15977,8 +15942,6 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16029,8 +15992,6 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16183,8 +16144,6 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16235,8 +16194,6 @@
           <t>NODE_S1999_00_0064</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16428,7 +16385,6 @@
           <t>NODE_S1999_00_0079</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16539,8 +16495,6 @@
           <t>NODE_S1999_00_0076</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16591,8 +16545,6 @@
           <t>NODE_S1999_00_0076</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16737,7 +16689,6 @@
           <t>NODE_S1999_00_0082</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>NODE_S1999_00_0087</t>
@@ -16793,7 +16744,6 @@
           <t>NODE_S1999_00_0082</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>NODE_S1999_00_0087</t>
@@ -16896,8 +16846,6 @@
           <t>NODE_S1999_00_0082</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17206,8 +17154,6 @@
           <t>NODE_S1999_00_0090</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17263,8 +17209,6 @@
           <t>NODE_S1999_00_0090</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17556,8 +17500,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -17687,7 +17629,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -35053,7 +34994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35233,6 +35174,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Sparta Praha</t>
         </is>
       </c>
     </row>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -42244,7 +42244,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M9" t="n">
         <v>16</v>
@@ -42463,7 +42463,7 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M12" t="n">
         <v>10</v>
@@ -42604,7 +42604,7 @@
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -42612,7 +42612,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -17500,6 +17500,8 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -17629,6 +17631,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19911,8 +19922,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20042,7 +20051,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -41984,7 +41992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42041,7 +42049,7 @@
           <t>CLUB_S1999_00_0004</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42061,7 +42069,7 @@
           <t>CLUB_S1999_00_0015</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42081,7 +42089,7 @@
           <t>CLUB_S1999_00_0027</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42101,7 +42109,7 @@
           <t>CLUB_S1999_00_0029</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42121,7 +42129,7 @@
           <t>CLUB_S1999_00_0034</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42141,7 +42149,7 @@
           <t>CLUB_S1999_00_0058</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -42161,7 +42169,7 @@
           <t>CLUB_S1999_00_0066</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42181,7 +42189,7 @@
           <t>CLUB_S1999_00_0069</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42201,7 +42209,7 @@
           <t>CLUB_S1999_00_0075</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42221,7 +42229,7 @@
           <t>CLUB_S1999_00_0082</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42241,7 +42249,7 @@
           <t>CLUB_S1999_00_0129</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42261,7 +42269,7 @@
           <t>CLUB_S1999_00_0141</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42281,7 +42289,7 @@
           <t>CLUB_S1999_00_0142</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42301,7 +42309,7 @@
           <t>CLUB_S1999_00_0209</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42321,7 +42329,7 @@
           <t>CLUB_S1999_00_0230</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -42341,7 +42349,7 @@
           <t>CLUB_S1999_00_0232</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42361,7 +42369,7 @@
           <t>CLUB_S1999_00_0236</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -42381,7 +42389,7 @@
           <t>CLUB_S1999_00_0238</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42401,7 +42409,7 @@
           <t>CLUB_S1999_00_0243</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -42421,7 +42429,7 @@
           <t>CLUB_S1999_00_0249</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -42441,7 +42449,7 @@
           <t>CLUB_S1999_00_0263</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0291 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -42461,7 +42469,7 @@
           <t>CLUB_S1999_00_0270</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0316 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -42481,7 +42489,7 @@
           <t>CLUB_S1999_00_0275</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -42501,7 +42509,7 @@
           <t>CLUB_S1999_00_0307</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'Florida Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42521,7 +42529,7 @@
           <t>CLUB_S1999_00_0309</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1998_99_0446 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -42541,7 +42549,7 @@
           <t>CLUB_S1999_00_0348</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'Buly Centrum Kravaře' → 'Kravaře' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -42561,7 +42569,7 @@
           <t>NODE_S1999_00_0030</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  1.kolo'</t>
         </is>
@@ -42581,7 +42589,7 @@
           <t>NODE_S1999_00_0031</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  2.kolo'</t>
         </is>
@@ -42601,7 +42609,7 @@
           <t>NODE_S1999_00_0032</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
@@ -42621,11 +42629,115 @@
           <t>NODE_S1999_00_0033</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 semifinále · NODE_S1999_00_0079</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Slovan Louny – PSV Litoměřice, HC Stadion Teplice – Ústí nad Labem B), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 O 3.místo · NODE_S1999_00_0080</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (Louny – Ústí nad Labem B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>30_Severočeský L40 finále · NODE_S1999_00_0081</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Stadion Teplice – Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Středočeský – Regionální liga (Středočeský kraj) · NODE_S1999_00_0101</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Berounští Medvědi "B", TJ Tatran Sedlčany), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F31"/>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14296,7 +14299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14752,6 +14755,74 @@
         </is>
       </c>
       <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0079</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Slovan Louny – PSV Litoměřice, HC Stadion Teplice – Ústí nad Labem B), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0080</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (Louny – Ústí nad Labem B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0081</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Stadion Teplice – Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NODE_S1999_00_0101</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Berounští Medvědi "B", TJ Tatran Sedlčany), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -42649,7 +42720,7 @@
           <t>30_Severočeský L40 semifinále · NODE_S1999_00_0079</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (Slovan Louny – PSV Litoměřice, HC Stadion Teplice – Ústí nad Labem B), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -42675,7 +42746,7 @@
           <t>30_Severočeský L40 O 3.místo · NODE_S1999_00_0080</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>máme jen 1 tým (Louny – Ústí nad Labem B), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -42701,7 +42772,7 @@
           <t>30_Severočeský L40 finále · NODE_S1999_00_0081</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Stadion Teplice – Litoměřice), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -42727,7 +42798,7 @@
           <t>Středočeský – Regionální liga (Středočeský kraj) · NODE_S1999_00_0101</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Berounští Medvědi "B", TJ Tatran Sedlčany), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -16514,7 +16514,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  1.kolo</t>
+          <t>KVAL 1.kolo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  2.kolo</t>
+          <t>KVAL 2.kolo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KVAL  skupina A</t>
+          <t>KVAL skupina A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KVAL  skupina B</t>
+          <t>KVAL skupina B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Praha L40 Pražský přebor</t>
+          <t>Praha, 4. úroveň Pražský přebor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -16885,7 +16885,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Praha L40 finále</t>
+          <t>Praha, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Praha L40 o umístění</t>
+          <t>Praha, 4. úroveň o umístění</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální liga</t>
+          <t>Středočeský, 4. úroveň Regionální liga</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finále</t>
+          <t>Středočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 o udržení</t>
+          <t>Středočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální soutěž</t>
+          <t>Středočeský, 4. úroveň Regionální soutěž</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17813,7 +17813,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -17962,7 +17962,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Čtvrtfinále</t>
+          <t>Jihočeský, 4. úroveň, Čtvrtfinále</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Semifinále</t>
+          <t>Jihočeský, 4. úroveň, Semifinále</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Krajská Soutěž</t>
+          <t>Jihočeský, 4. úroveň Krajská Soutěž</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -18263,7 +18263,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 Krajská soutěž</t>
+          <t>Západočeský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina Plzeň Jih</t>
+          <t>Západočeský, 4. úroveň, skupina Plzeň Jih</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 základní skupina</t>
+          <t>Západočeský, 4. úroveň, základní skupina</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -18412,7 +18412,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 finále</t>
+          <t>Západočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 o udržení</t>
+          <t>Západočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina Tachov</t>
+          <t>Západočeský, 4. úroveň, skupina Tachov</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -18554,7 +18554,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 základní skupina</t>
+          <t>Západočeský, 4. úroveň, základní skupina</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 finále</t>
+          <t>Západočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 o udržení</t>
+          <t>Západočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina Cheb -K.Vary</t>
+          <t>Západočeský, 4. úroveň, skupina Cheb -K.Vary</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -18803,7 +18803,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 základní část</t>
+          <t>Severočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 semifinále</t>
+          <t>Severočeský, 4. úroveň, semifinále</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -18965,7 +18965,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 O 3.místo</t>
+          <t>Severočeský, 4. úroveň O 3.místo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 finále</t>
+          <t>Severočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -19112,7 +19112,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -19159,7 +19159,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 základní část-sever</t>
+          <t>Východočeský, 4. úroveň, základní část-sever</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 základní část-jih</t>
+          <t>Východočeský, 4. úroveň, základní část-jih</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finálová skupina</t>
+          <t>Východočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 o udržení</t>
+          <t>Východočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 KS II.třídy</t>
+          <t>Východočeský, 4. úroveň KS II.třídy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 KS III.třídy</t>
+          <t>Východočeský, 4. úroveň KS III.třídy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Základní část</t>
+          <t>Jihomoravský, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -19679,7 +19679,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení</t>
+          <t>Jihomoravský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 II.třída</t>
+          <t>Jihomoravský, 4. úroveň II.třída</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -19776,7 +19776,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B1</t>
+          <t>Jihomoravský, 4. úroveň, skupina B1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B2</t>
+          <t>Jihomoravský, 4. úroveň, skupina B2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -19907,7 +19907,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -19954,7 +19954,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -19993,6 +19993,8 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20025,7 +20027,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -20122,6 +20124,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S1999_00_FINAL.xlsx
+++ b/data/S1999_00_FINAL.xlsx
@@ -3492,7 +3492,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -19993,8 +19993,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20124,7 +20122,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -43117,7 +43114,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -43195,7 +43192,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -43278,7 +43275,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -43356,7 +43353,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -43434,7 +43431,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -43512,7 +43509,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -43590,7 +43587,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -43673,7 +43670,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -43751,7 +43748,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -43829,7 +43826,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -43907,7 +43904,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -43985,7 +43982,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -44063,7 +44060,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -44146,7 +44143,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -44596,7 +44593,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -44674,7 +44671,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -44747,7 +44744,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -44825,7 +44822,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -44981,7 +44978,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -45096,7 +45093,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -45174,7 +45171,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -45252,7 +45249,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -52788,7 +52785,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -52866,7 +52863,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -52944,7 +52941,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -61202,7 +61199,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -61358,7 +61355,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -61436,7 +61433,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -62219,7 +62216,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -62297,7 +62294,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -62375,7 +62372,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -62531,7 +62528,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
